--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,49 +531,49 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5b8a36a5afef54</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -596,12 +596,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
@@ -636,84 +636,84 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Data Science &amp; AI</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Spark</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e5dda0d2bba57a</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - LLMOps &amp; MLOps</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e22c1fd4484e75</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Kafka, PostgreSQL, ETL, dbt, Power BI, Tableau, Terraform</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,137 +986,137 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Digital Data Architect</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4add298bd9de4d12</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Autonomous Vehicles)</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f30118514c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Henderson Brothers Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395d8b36121158cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,129 +1336,129 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>API Developer - Sr Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Warehouse ETL Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
+          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,332 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Falcon Fusion Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>API Developer - Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=791723a93998248e</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Data Warehouse ETL Developer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Ops Solution Developer II</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Impala, Scala, Oracle, SQL Server, ETL, Pentaho, Tableau</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a843f2e572d01441</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,154 +776,154 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,242 +986,242 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Henderson Brothers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42057f538af783d</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,94 +1336,94 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>API Developer - Sr Software Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Warehouse ETL Developer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ddce11ca45a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,227 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>API Developer - Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cecd23c45b016d</t>
+          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Tableau, Splunk, CI/CD, GitHub Actions, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ffeae73f778fcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,42 +1213,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, ETL, Splunk, GitHub Actions, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bdfce459e149d</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,87 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40494b4ecc16d393</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>API Developer - Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c28bf17a880cb1a7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,24 +1046,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, GCP, CI/CD, AWS CodePipeline, CodeBuild</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259990ef107da39</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,42 +1178,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1685,41 +1685,6 @@
         </is>
       </c>
       <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,77 +503,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Senior Backend Engineer - Startup</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>PROJITT LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -596,12 +596,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
@@ -636,49 +636,49 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
+          <t>Software Engineer III- DevOps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
+          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Data Operations</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54227ad96f5d5d38</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=51a019ac629e7fd8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,87 +1291,87 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
+          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,77 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
+          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Celebration, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Cloud Architecture, Workflow Automation &amp; Systems Integration)</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Metropolitan Transportation Authority</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf8c642c375c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PROJITT LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -596,89 +596,89 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III- DevOps</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b9b4aa91a59247</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,154 +1021,154 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a019ac629e7fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,462 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Paychex, Inc.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, dbt</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>API Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Falcon Fusion Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53fd7ffe892187b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, Splunk, Docker</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d14bdf995edae51e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -1238,7 +1238,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -561,12 +561,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
@@ -601,49 +601,49 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,50 +828,50 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,32 +898,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,137 +1056,137 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,40 +1266,355 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cloud AI Consultant</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>API Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Falcon Fusion Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>CA, US USA</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D34" t="n">
         <v>10.4</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 1</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, RDS, Databricks, Hive, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
+          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -561,12 +561,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
         </is>
       </c>
     </row>
@@ -601,49 +601,49 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,25 +758,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
         </is>
       </c>
     </row>
@@ -811,84 +811,84 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,24 +906,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,15 +1108,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Cloud AI Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud AI Consultant</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1580,41 +1580,6 @@
         </is>
       </c>
       <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud AI Consultant</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,24 +1431,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Cloud AI Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,84 +531,84 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1c1e8c1f767d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f4d600520d0e96</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418b09b41502f7df</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,32 +653,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,50 +688,50 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,50 +793,50 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,15 +1003,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Cloud AI Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,24 +1396,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1475,111 +1475,6 @@
         </is>
       </c>
       <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Cloud AI Consultant</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
         </is>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Backend Engineer - Startup</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PROJITT LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,32 +653,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,50 +688,50 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,50 +793,50 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,15 +1108,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=51a019ac629e7fd8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,164 +1186,164 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,42 +1353,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud AI Consultant</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,262 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>API Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Falcon Fusion Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CrowdStrike GenAI Security Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Cloud AI Consultant</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PROJITT LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4e2ae841a0e1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,32 +688,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,32 +758,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,50 +793,50 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,49 +986,49 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,124 +1056,124 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a019ac629e7fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,28 +1182,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,427 +1301,42 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Cloud AI Application Administrator</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>API Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Falcon Fusion Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Cloud AI Consultant</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,32 +478,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
+          <t>https://www.indeed.com/viewjob?jk=db40aa076d14f9d0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=28e4d6385751ba88</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,50 +758,50 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,32 +828,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,32 +898,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,50 +933,50 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,81 +1042,81 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,84 +1126,84 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,40 +1301,460 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Audacy, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>API Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Falcon Fusion Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>CA, US USA</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D38" t="n">
         <v>10.4</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -608,7 +608,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,24 +976,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -1448,7 +1448,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -993,7 +993,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e4d6385751ba88</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,24 +626,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=28e4d6385751ba88</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,32 +758,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,49 +811,49 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,49 +916,49 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Senior Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,24 +1011,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,24 +1046,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1112,28 +1112,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,49 +1161,49 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,32 +1213,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,84 +1371,84 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,120 +1458,120 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,29 +1646,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,332 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>API Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Falcon Fusion Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CrowdStrike GenAI Security Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cloud AI Consultant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-08.xlsx
+++ b/results/job_matches_2026-03-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40aa076d14f9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e73b6b4f92a343</t>
+          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,32 +583,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,32 +618,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eed21330f07799b</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,32 +653,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a426fbf9b09b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e4d6385751ba88</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,32 +723,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eb14a985ec302b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,32 +758,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd36b3af081d974a</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,50 +898,50 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack Web Developer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104dfb98c80f44fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,24 +1011,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,15 +1038,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1112,28 +1112,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,84 +1161,84 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer – (Systems Engineering, Enterprise Infra &amp; Platform Support) *HYBRID*</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c197bc54e43635</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Sr. Software Systems &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,28 +1252,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,50 +1283,50 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Audacy, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,49 +1336,49 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>API Enablement Specialist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,207 +1388,207 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07730b1f5d6d529d</t>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Systems &amp; Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f045bd52323b67</t>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31813beeef70938d</t>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2680cd4cb9c331ec</t>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
+          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Technical Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,392 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>API Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Falcon Fusion Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72174a3cd5d64195</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c27bc0cbf92e5826</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8710c024486747ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4ddd4ed5ac47a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbc3103892741b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Cloud AI Consultant</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
         </is>
       </c>
     </row>
